--- a/docentes/Santiago Hernández Mariana - Estadisticos 20211.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -70,58 +70,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>RUGERIO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIÑONES</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
   </si>
   <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ANGELINA</t>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>JAIME</t>
   </si>
   <si>
     <t>LUIS REY</t>
   </si>
   <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>FLOR GUADALUPE</t>
+    <t>NATALIE</t>
   </si>
   <si>
     <t>JAZMIN</t>
   </si>
   <si>
-    <t>KIMBERLY</t>
+    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
@@ -522,19 +507,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>67.44</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -548,19 +533,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>68.97</v>
+        <v>79.31</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -613,16 +598,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>55.81</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -636,16 +624,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>62.07</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -698,19 +689,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>67.44</v>
+        <v>83.72</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -724,19 +715,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>68.97</v>
+        <v>79.31</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -778,16 +769,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920088</v>
+        <v>21330051920096</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -796,7 +787,7 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -807,10 +798,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -819,44 +810,44 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920104</v>
+        <v>21330051920120</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920387</v>
+        <v>21330051920097</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -865,53 +856,30 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920097</v>
+        <v>21330051920133</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920383</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Santiago Hernández Mariana - Estadisticos 20211.xlsx
+++ b/docentes/Santiago Hernández Mariana - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
   <si>
     <t>Mat</t>
   </si>
@@ -70,43 +70,91 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CABALLERO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>TENTZOHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PELLICO</t>
+    <t>MOSTRANZO</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>LEÓN</t>
+  </si>
+  <si>
+    <t>ZALAVA</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>LUIS ARMANDO</t>
+  </si>
+  <si>
+    <t>JAZMIN ADALI</t>
+  </si>
+  <si>
+    <t>INGRID AMERICA</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>CARLOS URIEL</t>
   </si>
   <si>
     <t>NATALIE</t>
   </si>
   <si>
-    <t>JAZMIN</t>
+    <t>THANIA CRISTAL</t>
   </si>
   <si>
     <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>FERGIE PAULETTE</t>
   </si>
 </sst>
 </file>
@@ -598,19 +646,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>55.81</v>
+        <v>74.42</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -624,19 +672,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>62.07</v>
+        <v>75.86</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -692,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>83.72</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -718,16 +766,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>79.31</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -769,16 +817,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920096</v>
+        <v>21330051920357</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -792,16 +840,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920099</v>
+        <v>21330051920389</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -815,25 +863,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920120</v>
+        <v>21330051920094</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -844,10 +892,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -861,25 +909,140 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920133</v>
+        <v>21330051920107</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920110</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920120</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920128</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G6">
-        <v>3</v>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920073</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
